--- a/src/out_live.xlsx
+++ b/src/out_live.xlsx
@@ -427,7 +427,7 @@
         <v>Game ID</v>
       </c>
       <c r="B3" t="str">
-        <v>mt3d0cbhv7chms</v>
+        <v>mt3dhuywvkkz2t</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>Exported</v>
       </c>
       <c r="B17" t="str">
-        <v>8/21/2026, 1:45:50 PM</v>
+        <v>8/21/2026, 1:59:27 PM</v>
       </c>
     </row>
   </sheetData>

--- a/src/out_live.xlsx
+++ b/src/out_live.xlsx
@@ -427,7 +427,7 @@
         <v>Game ID</v>
       </c>
       <c r="B3" t="str">
-        <v>mt3dhuywvkkz2t</v>
+        <v>mt7qnwun9l8tq8</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>Date</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-24</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>Opponent goals</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -507,7 +507,7 @@
         <v>Halftime</v>
       </c>
       <c r="B13" t="str">
-        <v>3-1</v>
+        <v>3-2</v>
       </c>
     </row>
     <row r="14">
@@ -539,7 +539,7 @@
         <v>Exported</v>
       </c>
       <c r="B17" t="str">
-        <v>8/21/2026, 1:59:27 PM</v>
+        <v>8/24/2026, 3:19:10 PM</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:S15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -571,6 +571,7 @@
     <col min="16" max="16" width="9.83203125" customWidth="1"/>
     <col min="17" max="17" width="9.83203125" customWidth="1"/>
     <col min="18" max="18" width="9.83203125" customWidth="1"/>
+    <col min="19" max="19" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,48 +585,51 @@
         <v>Pos</v>
       </c>
       <c r="D1" t="str">
+        <v>Minutes</v>
+      </c>
+      <c r="E1" t="str">
         <v>Goals</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Shots</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Shot %</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Assists</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Steals</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Blocks</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Turnovers</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>7's Drawn</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>7's Made</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>7's Missed</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2 Min</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>2's Drawn</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Yellow</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Red</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Points</v>
       </c>
     </row>
@@ -640,17 +644,17 @@
         <v>CB</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0.04</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
         <v>100</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
         <v>0</v>
       </c>
@@ -682,6 +686,9 @@
         <v>0</v>
       </c>
       <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>2</v>
       </c>
     </row>
@@ -696,20 +703,20 @@
         <v>LB</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
       <c r="I3">
         <v>0</v>
       </c>
@@ -729,15 +736,18 @@
         <v>0</v>
       </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>1</v>
       </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>1</v>
       </c>
     </row>
@@ -752,17 +762,17 @@
         <v>RW</v>
       </c>
       <c r="D4">
+        <v>0.04</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>2</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>50</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
         <v>0</v>
       </c>
@@ -773,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -782,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -794,6 +804,9 @@
         <v>0</v>
       </c>
       <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>1</v>
       </c>
     </row>
@@ -808,16 +821,16 @@
         <v>P</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5">
-        <v>0</v>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
       </c>
       <c r="H5">
         <v>0</v>
@@ -850,6 +863,9 @@
         <v>0</v>
       </c>
       <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>0</v>
       </c>
     </row>
@@ -869,11 +885,11 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6">
-        <v>0</v>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
       </c>
       <c r="H6">
         <v>0</v>
@@ -906,6 +922,9 @@
         <v>0</v>
       </c>
       <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>0</v>
       </c>
     </row>
@@ -920,16 +939,16 @@
         <v>RB</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7">
-        <v>0</v>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
       </c>
       <c r="H7">
         <v>0</v>
@@ -950,11 +969,11 @@
         <v>0</v>
       </c>
       <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
         <v>1</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
       <c r="P7">
         <v>0</v>
       </c>
@@ -962,6 +981,9 @@
         <v>0</v>
       </c>
       <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>0</v>
       </c>
     </row>
@@ -976,23 +998,23 @@
         <v>LB</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8">
-        <v>0</v>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
       </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>1</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
       <c r="J8">
         <v>0</v>
       </c>
@@ -1018,6 +1040,9 @@
         <v>0</v>
       </c>
       <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>0</v>
       </c>
     </row>
@@ -1037,11 +1062,11 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9">
-        <v>0</v>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1074,6 +1099,9 @@
         <v>0</v>
       </c>
       <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>0</v>
       </c>
     </row>
@@ -1093,11 +1121,11 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10">
-        <v>0</v>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1130,6 +1158,9 @@
         <v>0</v>
       </c>
       <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>0</v>
       </c>
     </row>
@@ -1149,11 +1180,11 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11">
-        <v>0</v>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1186,6 +1217,9 @@
         <v>0</v>
       </c>
       <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>0</v>
       </c>
     </row>
@@ -1200,16 +1234,16 @@
         <v>GK</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12">
-        <v>0</v>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1242,6 +1276,9 @@
         <v>0</v>
       </c>
       <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>0</v>
       </c>
     </row>
@@ -1261,11 +1298,11 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13">
-        <v>0</v>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1298,6 +1335,9 @@
         <v>0</v>
       </c>
       <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>0</v>
       </c>
     </row>
@@ -1317,11 +1357,11 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14">
-        <v>0</v>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1354,6 +1394,9 @@
         <v>0</v>
       </c>
       <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>0</v>
       </c>
     </row>
@@ -1367,29 +1410,29 @@
       <c r="C15" t="str">
         <v/>
       </c>
-      <c r="D15">
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15">
         <v>3</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>4</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>75</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -1404,25 +1447,28 @@
         <v>1</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15">
         <v>0</v>
       </c>
       <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -1433,6 +1479,7 @@
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1463,6 +1510,9 @@
       <c r="I1" t="str">
         <v>Saves After Whistle</v>
       </c>
+      <c r="J1" t="str">
+        <v>Empty Net Goals</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1492,10 +1542,13 @@
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1528,7 +1581,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1539,7 +1592,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1550,7 +1603,7 @@
         <v>75</v>
       </c>
       <c r="C4">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -1650,7 +1703,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K22"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" customWidth="1"/>
@@ -1708,7 +1761,7 @@
         <v>H1</v>
       </c>
       <c r="C2" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D2" t="str">
         <v>Air Force</v>
@@ -1743,7 +1796,7 @@
         <v>H1</v>
       </c>
       <c r="C3" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D3" t="str">
         <v>Air Force</v>
@@ -1778,7 +1831,7 @@
         <v>H1</v>
       </c>
       <c r="C4" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D4" t="str">
         <v>Air Force</v>
@@ -1813,25 +1866,25 @@
         <v>H1</v>
       </c>
       <c r="C5" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D5" t="str">
         <v>Air Force</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F5" t="str">
-        <v>Ryan</v>
+        <v>Sean</v>
       </c>
       <c r="G5" t="str">
-        <v>7m GOAL</v>
+        <v>to the bench</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>3-0</v>
+        <v>2-0</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1848,7 +1901,7 @@
         <v>H1</v>
       </c>
       <c r="C6" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D6" t="str">
         <v>Air Force</v>
@@ -1860,13 +1913,13 @@
         <v>Ryan</v>
       </c>
       <c r="G6" t="str">
-        <v>7m drawn</v>
+        <v>on the court</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>3-0</v>
+        <v>2-0</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1883,25 +1936,25 @@
         <v>H1</v>
       </c>
       <c r="C7" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D7" t="str">
         <v>Air Force</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F7" t="str">
-        <v>Evan</v>
+        <v>Charlie</v>
       </c>
       <c r="G7" t="str">
-        <v>2-minute</v>
+        <v>to the bench</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>3-0</v>
+        <v>2-0</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -1918,25 +1971,25 @@
         <v>H1</v>
       </c>
       <c r="C8" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D8" t="str">
         <v>Air Force</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F8" t="str">
-        <v>Barrett</v>
+        <v>Evan</v>
       </c>
       <c r="G8" t="str">
-        <v>steal</v>
+        <v>on the court</v>
       </c>
       <c r="H8" t="str">
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>3-0</v>
+        <v>2-0</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1953,25 +2006,25 @@
         <v>H1</v>
       </c>
       <c r="C9" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D9" t="str">
         <v>Air Force</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F9" t="str">
-        <v>RJ</v>
+        <v>Ben</v>
       </c>
       <c r="G9" t="str">
-        <v>drew a 2-minute</v>
+        <v>to the bench</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>3-0</v>
+        <v>2-0</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -1988,25 +2041,25 @@
         <v>H1</v>
       </c>
       <c r="C10" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D10" t="str">
-        <v>Army</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
+        <v>Air Force</v>
+      </c>
+      <c r="E10">
+        <v>21</v>
       </c>
       <c r="F10" t="str">
-        <v>Army</v>
+        <v>Barrett</v>
       </c>
       <c r="G10" t="str">
-        <v>GOAL</v>
+        <v>on the court</v>
       </c>
       <c r="H10" t="str">
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>3-1</v>
+        <v>2-0</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -2023,25 +2076,25 @@
         <v>H1</v>
       </c>
       <c r="C11" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D11" t="str">
-        <v>Army</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
+        <v>Air Force</v>
+      </c>
+      <c r="E11">
+        <v>23</v>
       </c>
       <c r="F11" t="str">
-        <v>Army</v>
+        <v>Ryan</v>
       </c>
       <c r="G11" t="str">
-        <v>shot saved — Air Force save</v>
+        <v>7m GOAL</v>
       </c>
       <c r="H11" t="str">
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>3-1</v>
+        <v>3-0</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -2058,25 +2111,25 @@
         <v>H1</v>
       </c>
       <c r="C12" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D12" t="str">
-        <v>Army</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
+        <v>Air Force</v>
+      </c>
+      <c r="E12">
+        <v>23</v>
       </c>
       <c r="F12" t="str">
-        <v>Army</v>
+        <v>Ryan</v>
       </c>
       <c r="G12" t="str">
-        <v>save after the whistle</v>
+        <v>7m drawn</v>
       </c>
       <c r="H12" t="str">
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>3-1</v>
+        <v>3-0</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -2093,25 +2146,25 @@
         <v>H1</v>
       </c>
       <c r="C13" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D13" t="str">
         <v>Air Force</v>
       </c>
-      <c r="E13" t="str">
-        <v/>
+      <c r="E13">
+        <v>18</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>Evan</v>
       </c>
       <c r="G13" t="str">
-        <v>note</v>
+        <v>2-minute</v>
       </c>
       <c r="H13" t="str">
-        <v>Momentum swing after the steal</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>3-1</v>
+        <v>3-0</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -2128,31 +2181,31 @@
         <v>H1</v>
       </c>
       <c r="C14" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D14" t="str">
-        <v>Army</v>
-      </c>
-      <c r="E14" t="str">
-        <v>9</v>
+        <v>Air Force</v>
+      </c>
+      <c r="E14">
+        <v>21</v>
       </c>
       <c r="F14" t="str">
-        <v>Army</v>
+        <v>Barrett</v>
       </c>
       <c r="G14" t="str">
-        <v>shot saved — Air Force save</v>
+        <v>steal</v>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>3-1</v>
-      </c>
-      <c r="J14">
-        <v>30</v>
-      </c>
-      <c r="K14">
-        <v>62</v>
+        <v>3-0</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -2163,43 +2216,288 @@
         <v>H1</v>
       </c>
       <c r="C15" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D15" t="str">
         <v>Air Force</v>
       </c>
       <c r="E15">
+        <v>11</v>
+      </c>
+      <c r="F15" t="str">
+        <v>RJ</v>
+      </c>
+      <c r="G15" t="str">
+        <v>drew a 2-minute</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>3-0</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>H1</v>
+      </c>
+      <c r="C16" t="str">
+        <v>30:00</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Army</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>Army</v>
+      </c>
+      <c r="G16" t="str">
+        <v>GOAL</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>3-1</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>H1</v>
+      </c>
+      <c r="C17" t="str">
+        <v>30:00</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Army</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>Army</v>
+      </c>
+      <c r="G17" t="str">
+        <v>shot saved — Air Force save</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>3-1</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>H1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>30:00</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Army</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>Army</v>
+      </c>
+      <c r="G18" t="str">
+        <v>save after the whistle</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>3-1</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>H1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>30:00</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Air Force</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v>note</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Momentum swing after the steal</v>
+      </c>
+      <c r="I19" t="str">
+        <v>3-1</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>H1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>30:00</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Army</v>
+      </c>
+      <c r="E20" t="str">
+        <v>9</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Army</v>
+      </c>
+      <c r="G20" t="str">
+        <v>shot saved — Air Force save</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>3-1</v>
+      </c>
+      <c r="J20">
+        <v>30</v>
+      </c>
+      <c r="K20">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>H1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>30:00</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Air Force</v>
+      </c>
+      <c r="E21">
         <v>23</v>
       </c>
-      <c r="F15" t="str">
+      <c r="F21" t="str">
         <v>Ryan</v>
       </c>
-      <c r="G15" t="str">
+      <c r="G21" t="str">
         <v>7m missed</v>
       </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
         <v>3-1</v>
       </c>
-      <c r="J15">
+      <c r="J21">
         <v>50</v>
       </c>
-      <c r="K15">
-        <v>11.9</v>
+      <c r="K21">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>H1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>30:00</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Army</v>
+      </c>
+      <c r="E22" t="str">
+        <v>4</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Army</v>
+      </c>
+      <c r="G22" t="str">
+        <v>GOAL</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>3-2</v>
+      </c>
+      <c r="J22">
+        <v>40</v>
+      </c>
+      <c r="K22">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L4"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" customWidth="1"/>
@@ -2246,6 +2544,9 @@
         <v>Y %</v>
       </c>
       <c r="K1" t="str">
+        <v>Note</v>
+      </c>
+      <c r="L1" t="str">
         <v>(X/Y are % of the goal-map image, from the keeper's left)</v>
       </c>
     </row>
@@ -2257,7 +2558,7 @@
         <v>H1</v>
       </c>
       <c r="C2" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D2" t="str">
         <v>Army</v>
@@ -2292,7 +2593,7 @@
         <v>H1</v>
       </c>
       <c r="C3" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D3" t="str">
         <v>Air Force</v>
@@ -2313,15 +2614,50 @@
         <v>50</v>
       </c>
       <c r="J3">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="K3" t="str">
         <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>H1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>30:00</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Army</v>
+      </c>
+      <c r="E4" t="str">
+        <v>4</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Army</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Goal</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4">
+        <v>40</v>
+      </c>
+      <c r="J4">
+        <v>45</v>
+      </c>
+      <c r="K4" t="str">
+        <v>EMPTY NET</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
